--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="C10" s="31" t="n">
-        <v>5.963</v>
+        <v>6.1481</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>**第9期計画の公表値から逆算した小野町の実績値。**（①＋③）×23％＋（①＋③）×5％－保険料収納必要額832,562千円 より5.963％。後期高齢者加入割合が高く低所得層が厚い保険者ほど5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する**</t>
+          <t>**第9期計画の公表値から逆算した小野町の実績値。**（①＋②）×23％＋（①＋③）×5％－保険料収納必要額832,562千円＝219,272千円。これを①で割って6.148％。**基数に総合事業費を含めない**（見える化システムの算式。含めると5.963％で、見込額そのものは変わらない）。後期高齢者加入割合が高く低所得層が厚い保険者ほど5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する**</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="C11" s="22">
-        <f>(C2+C4)*C10/100</f>
+        <f>C2*C10/100</f>
         <v/>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>（①＋③）×⑨</t>
+          <t>**①×⑨。⑧と違い基数に③総合事業費を含めない（見える化システムの算式）**</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -226,6 +226,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1160,7 +1163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1397,7 +1400,7 @@
         </is>
       </c>
       <c r="C10" s="31" t="n">
-        <v>6.1481</v>
+        <v>5.5332</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
@@ -1406,7 +1409,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>**第9期計画の公表値から逆算した小野町の実績値。**（①＋②）×23％＋（①＋③）×5％－保険料収納必要額832,562千円＝219,272千円。これを①で割って6.148％。**基数に総合事業費を含めない**（見える化システムの算式。含めると5.963％で、見込額そのものは変わらない）。後期高齢者加入割合が高く低所得層が厚い保険者ほど5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する**</t>
+          <t>**算式で求めた値。（第1号被保険者負担割合＋5％）－第1号被保険者負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数。**後期高齢者加入割合補正係数は見える化ワークシート（5_保険料推計 96行）の令和9年度0.9558・令和10年度0.9802・令和11年度1.0065、所得段階別加入割合補正係数は0.9959。年度別では6.107％・5.548％・4.945％で、その平均。**基数に総合事業費を含めない**（見える化システムの算式）。第9期計画の公表値では調整交付金見込額216,070千円÷標準給付費見込額3,566,486千円＝6.058％で、同じ算式に補正係数0.974を入れると整合する。**第10期の値は見える化システムの係数シート（全国値）で確認する**</t>
         </is>
       </c>
     </row>
@@ -1724,6 +1727,7 @@
       <c r="C24" s="17" t="n"/>
       <c r="D24" s="17" t="n"/>
       <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="34" t="inlineStr">
@@ -1738,7 +1742,7 @@
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>保険料率</t>
+          <t>標準割合（算定用）</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
@@ -1749,6 +1753,11 @@
       <c r="E25" s="34" t="inlineStr">
         <is>
           <t>補正後人数</t>
+        </is>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>賦課割合（軽減後）</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1773,7 @@
         </is>
       </c>
       <c r="C26" s="31" t="n">
-        <v>0.285</v>
+        <v>0.455</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>1568</v>
@@ -1773,6 +1782,9 @@
         <f>IF(D26="","",C26*D26)</f>
         <v/>
       </c>
+      <c r="F26" s="36" t="n">
+        <v>0.285</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1786,7 +1798,7 @@
         </is>
       </c>
       <c r="C27" s="31" t="n">
-        <v>0.486</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>887</v>
@@ -1795,6 +1807,9 @@
         <f>IF(D27="","",C27*D27)</f>
         <v/>
       </c>
+      <c r="F27" s="36" t="n">
+        <v>0.486</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1808,7 +1823,7 @@
         </is>
       </c>
       <c r="C28" s="31" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>812</v>
@@ -1817,6 +1832,9 @@
         <f>IF(D28="","",C28*D28)</f>
         <v/>
       </c>
+      <c r="F28" s="36" t="n">
+        <v>0.6850000000000001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1839,6 +1857,9 @@
         <f>IF(D29="","",C29*D29)</f>
         <v/>
       </c>
+      <c r="F29" s="36" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -1861,6 +1882,9 @@
         <f>IF(D30="","",C30*D30)</f>
         <v/>
       </c>
+      <c r="F30" s="36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -1883,6 +1907,9 @@
         <f>IF(D31="","",C31*D31)</f>
         <v/>
       </c>
+      <c r="F31" s="36" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -1905,6 +1932,9 @@
         <f>IF(D32="","",C32*D32)</f>
         <v/>
       </c>
+      <c r="F32" s="36" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1927,6 +1957,9 @@
         <f>IF(D33="","",C33*D33)</f>
         <v/>
       </c>
+      <c r="F33" s="36" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1949,6 +1982,9 @@
         <f>IF(D34="","",C34*D34)</f>
         <v/>
       </c>
+      <c r="F34" s="36" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1971,6 +2007,9 @@
         <f>IF(D35="","",C35*D35)</f>
         <v/>
       </c>
+      <c r="F35" s="36" t="n">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -1993,6 +2032,9 @@
         <f>IF(D36="","",C36*D36)</f>
         <v/>
       </c>
+      <c r="F36" s="36" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -2015,6 +2057,9 @@
         <f>IF(D37="","",C37*D37)</f>
         <v/>
       </c>
+      <c r="F37" s="36" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -2036,6 +2081,9 @@
       <c r="E38" s="21">
         <f>IF(D38="","",C38*D38)</f>
         <v/>
+      </c>
+      <c r="F38" s="36" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="39">
@@ -2054,11 +2102,12 @@
         <f>SUM(E26:E38)</f>
         <v/>
       </c>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>※ **保険料率は小野町が第9期で定めた割合（年報 様式1 所得段階別）。**第1〜3段階は国の標準（0.455／0.685／0.69）より低い0.285／0.486／0.685で、公費による低所得者軽減を反映した率です。第10期の段階設定は国の基本指針を受けて確定します。</t>
+          <t>※ **算定に用いる割合は、介護保険法施行令第38条の標準段階の割合（0.455／0.685／0.690／0.9／1.0／1.2／1.3／1.5／1.7／1.9／2.1／2.3／2.4）です。**小野町が実際に賦課する割合は第1〜3段階が0.285／0.486／0.685で、公費による低所得者軽減強化を反映した後のものです（F列）。軽減相当額は国2分の1・県4分の1・町4分の1の公費で補填され、保険料収納必要額から控除されないため、**基準額の算定では軽減前を用います。**見える化システムの「①標準段階区分・割合を用いる場合の入力」の画面でも0.4550／0.6850／0.6900が固定で表示されます。</t>
         </is>
       </c>
     </row>
@@ -2072,14 +2121,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>※ 補正後人数＝保険料率×被保険者数。この合計÷被保険者数の合計が「所得段階別加入割合補正係数」で、調整交付金の算定にも用います。</t>
+          <t>※ 補正後人数＝標準割合×被保険者数。この合計÷被保険者数の合計が「所得段階別加入割合補正係数」で、調整交付金の算定にも用います。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>※ **第9期の算定における補正係数は0.968でしたが、令和7年度実績では0.952です。**低所得段階の割合が上がっており、同じ賦課総額でも基準額が上がる方向に働きます。第9期の算定に用いた所得段階別人数の年度を町に確認してください。</t>
+          <t>※ **令和7年度末の構成による補正係数は0.9959です。**第9期計画は補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.9738で、当時の9段階の構成に標準割合を当てたものと整合します。</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2210,7 @@
           <t>C1 標準（低位）</t>
         </is>
       </c>
-      <c r="B2" s="36" t="n"/>
+      <c r="B2" s="37" t="n"/>
       <c r="C2" s="10" t="n"/>
       <c r="D2" s="10" t="n"/>
       <c r="E2" s="10" t="n"/>
@@ -2176,7 +2225,7 @@
           <t>C2 標準（高位）</t>
         </is>
       </c>
-      <c r="B3" s="36" t="n"/>
+      <c r="B3" s="37" t="n"/>
       <c r="C3" s="10" t="n"/>
       <c r="D3" s="10" t="n"/>
       <c r="E3" s="10" t="n"/>
@@ -2191,7 +2240,7 @@
           <t>C3 施設整備あり</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n"/>
+      <c r="B4" s="37" t="n"/>
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="10" t="n"/>
       <c r="E4" s="10" t="n"/>
@@ -2206,7 +2255,7 @@
           <t>C4 制度改正の影響</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
+      <c r="B5" s="37" t="n"/>
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="10" t="n"/>
@@ -2221,7 +2270,7 @@
           <t>C5 基金活用</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n"/>
+      <c r="B6" s="37" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="10" t="n"/>
@@ -2236,7 +2285,7 @@
           <t>C6 保険料据置（逆算）</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n"/>
+      <c r="B7" s="37" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="n"/>
@@ -2325,7 +2374,7 @@
           <t>要支援・要介護認定者数（令和8年3月末）</t>
         </is>
       </c>
-      <c r="C2" s="37" t="n">
+      <c r="C2" s="38" t="n">
         <v>792</v>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -3000,7 +3049,7 @@
           <t>収納率（現年度分）</t>
         </is>
       </c>
-      <c r="C29" s="38" t="n">
+      <c r="C29" s="39" t="n">
         <v>0.9935</v>
       </c>
       <c r="D29" s="8" t="inlineStr">

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
@@ -1169,8 +1169,9 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1808,7 +1809,7 @@
         <v/>
       </c>
       <c r="F27" s="36" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="28">
@@ -2107,7 +2108,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>※ **算定に用いる割合は、介護保険法施行令第38条の標準段階の割合（0.455／0.685／0.690／0.9／1.0／1.2／1.3／1.5／1.7／1.9／2.1／2.3／2.4）です。**小野町が実際に賦課する割合は第1〜3段階が0.285／0.486／0.685で、公費による低所得者軽減強化を反映した後のものです（F列）。軽減相当額は国2分の1・県4分の1・町4分の1の公費で補填され、保険料収納必要額から控除されないため、**基準額の算定では軽減前を用います。**見える化システムの「①標準段階区分・割合を用いる場合の入力」の画面でも0.4550／0.6850／0.6900が固定で表示されます。</t>
+          <t>※ **算定に用いる割合は、介護保険法施行令第38条の標準段階の割合（0.455／0.685／0.690／0.9／1.0／1.2／1.3／1.5／1.7／1.9／2.1／2.3／2.4）です。**小野町が実際に賦課する割合は第1〜3段階が0.285／0.485／0.685で、公費による低所得者軽減強化を反映した後のものです（F列）。軽減相当額は国2分の1・県4分の1・町4分の1の公費で補填され、保険料収納必要額から控除されないため、**基準額の算定では軽減前を用います。**見える化システムの「①標準段階区分・割合を用いる場合の入力」の画面でも0.4550／0.6850／0.6900が固定で表示されます。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
@@ -4299,7 +4299,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>※ 未利用者が利用に移行すると給付費が急増します。**未利用の理由は需要側が92.9％（状態ではない46.8％、本人希望なし29.2％、家族が介護16.9％）、供給制約は0.6％**であり、供給を増やしても利用は増えない構造です。</t>
+          <t>※ 未利用者が利用に移行すると給付費が急増します。**未利用の理由は上位3つが需要側（状態ではない46.8％、本人希望なし29.2％、家族が介護16.9％）、供給側の理由を挙げた方は1人**でした（複数回答・n=154）。**したがって、供給を増やすことが利用の増加に直結するとは見込めません。**</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量保険料算定シート_20260915.xlsx
@@ -1054,7 +1054,7 @@
       <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>**介護給付費準備基金の年度末残高。**年報 様式4 では令和4年度末120,000千円→令和5年度末12,000千円と10分の1になっているが、繰入金は全年度ゼロで矛盾する。基金運用状況調書での確認を要する</t>
+          <t>**介護給付費準備基金の令和7年度末の残高（財産に関する調書）。**令和5年度末120,000千円は町の財務書類で確認済み。令和8年度末見込は210,000千円</t>
         </is>
       </c>
       <c r="C43" s="2" t="n"/>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>**政策判断。第9期は35,000千円を見込んだが、介護給付費準備基金の保有額は令和5・6年度末とも12,000千円しかない（年報 様式4）。**しかも令和4年度末は120,000千円で、繰入金は全年度ゼロなのに残高が10分の1になっており、年報の系列自体に矛盾がある。**基金運用状況調書で残高を確認したうえで設定する。**ケースC5・C6で変える</t>
+          <t>**政策判断。第9期は35,000千円を見込んだ。介護給付費準備基金の残高は令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円。**ケースC5・C6で変える</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>※ 協議会に諮る際は、保険料の水準だけでなく、繰越金182.0百万円・基金純増88.1百万円という財政余剰の還元方針を併せて示します。</t>
+          <t>※ 協議会に諮る際は、保険料の水準だけでなく、繰越金182.0百万円・基金残高120.0百万円（令和5年度末）という財政余剰の還元方針を併せて示します。</t>
         </is>
       </c>
     </row>
@@ -3072,11 +3072,11 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>介護給付費準備基金 保有額（令和6年度末）</t>
+          <t>介護給付費準備基金 残高（令和5年度末）</t>
         </is>
       </c>
       <c r="C30" s="22" t="n">
-        <v>12000000</v>
+        <v>120000000</v>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>**年報 様式4。令和4年度末は120,000,000円で1桁違う。要確認**</t>
+          <t>町の財務書類（附属明細書「基金の明細」）。年報 様式4 の保有額は財務書類と合わない</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>繰越金182.0百万円・基金純増88.1百万円という財政余剰の還元。取崩額を変えて保険料への影響を示す</t>
+          <t>繰越金182.0百万円・基金残高120.0百万円（令和5年度末）という財政余剰の還元。取崩額を変えて保険料への影響を示す</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
